--- a/generated/spreadsheet/lawful-development-certficate-proposed-work-to-a-listed-building-ldc-proposed-work-lb.xlsx
+++ b/generated/spreadsheet/lawful-development-certficate-proposed-work-to-a-listed-building-ldc-proposed-work-lb.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,9 @@
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1413,13 +1413,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1448,13 +1452,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1478,14 +1486,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1509,19 +1525,19 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1531,58 +1547,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Telephone number and email address of the applicant.</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Telephone number and email address of the applicant.</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1606,18 +1622,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1627,7 +1639,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1646,18 +1658,18 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1667,47 +1679,51 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Name and contact information for the parties making the application.</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Applicants[]</t>
@@ -1715,18 +1731,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1736,7 +1748,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1767,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1771,7 +1783,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1790,13 +1802,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1825,13 +1837,13 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -1860,67 +1872,95 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1930,51 +1970,43 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Declaration</t>
+          <t>Conflict of interest</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Person reference</t>
-        </is>
-      </c>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1982,12 +2014,12 @@
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -1997,11 +2029,19 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Signed and dated verification of the application's accuracy.</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -2009,12 +2049,12 @@
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2024,19 +2064,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Description of proposed works for listed building lawful development certificate</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Details of development plans for the work to the listed building an applicant is seeking a lawful development certificate for</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Description of Proposed Works</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -2044,12 +2076,12 @@
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>A detailed description of the proposed works (including existing and proposed materials and finishes) together with details of those parts) of the building that are likely to be affected.</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2059,19 +2091,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Grounds for application</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Why a Certificate of Lawfulness of Propose Works is being requested.</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Grounds for application</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -2079,14 +2103,12 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason(s) why Certificate of Lawfulness of Proposed Works should be granted,
-including explanation of why listed building consent is not required
-</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2096,23 +2118,27 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Description of proposed works for listed building lawful development certificate</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Details of development plans for the work to the listed building an applicant is seeking a lawful development certificate for</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Supporting documents[]</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Description of Proposed Works</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A detailed description of the proposed works (including existing and proposed materials and finishes) together with details of those parts) of the building that are likely to be affected.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2129,17 +2155,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Interest details</t>
+          <t>Grounds for application</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+          <t>Why a Certificate of Lawfulness of Propose Works is being requested.</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest type</t>
+          <t>Grounds for application</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2147,12 +2173,14 @@
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>The applicant’s relationship to the land, property or building</t>
+          <t xml:space="preserve">Reason(s) why Certificate of Lawfulness of Proposed Works should be granted,
+including explanation of why listed building consent is not required
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2166,23 +2194,19 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
+          <t>Supporting documents[]</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2192,37 +2216,37 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Interest details</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+        </is>
+      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Applicant interest type</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The applicant’s relationship to the land, property or building</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2246,13 +2270,13 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2262,7 +2286,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2281,13 +2305,13 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2316,13 +2340,13 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2332,7 +2356,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2346,19 +2370,27 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Whether the owner has been informed of the application</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2372,7 +2404,7 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2382,13 +2414,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2407,7 +2443,7 @@
       <c r="B58" s="2" t="n"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2417,13 +2453,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2433,7 +2473,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2442,28 +2482,24 @@
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
+          <t>Informed of application</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Whether the owner has been informed of the application</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2487,13 +2523,13 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2503,7 +2539,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2522,13 +2558,13 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2538,7 +2574,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2552,14 +2588,18 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Nature of interest</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Description of the nature of a person's interest in the property</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -2583,19 +2623,27 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Whether the person has been informed of the application</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2614,14 +2662,22 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Reason not informed</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Reason why a person was not informed of the application</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -2636,37 +2692,41 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>The grade of any listed building affected by the proposed development.</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Listed building grade</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2675,15 +2735,19 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Listed building</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Nature of interest</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Listed building reference for cross-referencing with listed building records</t>
+          <t>Description of the nature of a person's interest in the property</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -2693,7 +2757,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2702,69 +2766,77 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Provided by</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Informed of application</t>
+        </is>
+      </c>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Source of the listed building grade information</t>
+          <t>Whether the person has been informed of the application</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Reason not informed</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Reason why a person was not informed of the application</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Listed building grade</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>The grade of any listed building affected by the proposed development.</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Listed building grade</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2772,17 +2844,17 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>The grade of the listed building, selected from the listed-building-grade codelist or "don't know"</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2863,7 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Listed building</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2799,7 +2871,7 @@
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Listed building reference for cross-referencing with listed building records</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -2818,7 +2890,7 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Provided by</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -2826,12 +2898,12 @@
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Source of the listed building grade information</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -2841,11 +2913,19 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="2" t="n"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Details of pre-application advice previously received from the planning authority</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2853,51 +2933,39 @@
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Where the proposed development will be built.</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Officer name</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -2911,19 +2979,15 @@
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -2942,24 +3006,20 @@
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -2973,24 +3033,20 @@
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3000,8 +3056,16 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Where the proposed development will be built.</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Site locations[]</t>
@@ -3009,24 +3073,24 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3040,24 +3104,28 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3071,19 +3139,23 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -3102,14 +3174,18 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3133,14 +3209,18 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3155,37 +3235,33 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Easting</t>
+        </is>
+      </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3194,25 +3270,29 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3221,20 +3301,24 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3248,55 +3332,59 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="2" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -3310,27 +3398,143 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -3338,36 +3542,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="B73:B81"/>
-    <mergeCell ref="A43"/>
+    <mergeCell ref="B49"/>
+    <mergeCell ref="A37:A43"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A82:A87"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A50:A64"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A68:A72"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="B47"/>
-    <mergeCell ref="B82:B87"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B43"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="B45"/>
+    <mergeCell ref="B52:B68"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="A49"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="A45"/>
+    <mergeCell ref="A86:A91"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B42"/>
-    <mergeCell ref="A73:A81"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="A77:A85"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B44"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="A52:A68"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A42"/>
-    <mergeCell ref="A47"/>
-    <mergeCell ref="B50:B64"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B77:B85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
